--- a/data/nzd0102/nzd0102.xlsx
+++ b/data/nzd0102/nzd0102.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I330"/>
+  <dimension ref="A1:I331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11314,6 +11314,39 @@
       <c r="I330" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>361.06</v>
+      </c>
+      <c r="C331" t="n">
+        <v>351.39</v>
+      </c>
+      <c r="D331" t="n">
+        <v>344.78</v>
+      </c>
+      <c r="E331" t="n">
+        <v>343.15</v>
+      </c>
+      <c r="F331" t="n">
+        <v>347.09</v>
+      </c>
+      <c r="G331" t="n">
+        <v>349.74</v>
+      </c>
+      <c r="H331" t="n">
+        <v>336.83</v>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B356"/>
+  <dimension ref="A1:B357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14891,6 +14924,16 @@
       </c>
       <c r="B356" t="n">
         <v>-0.37</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>
@@ -15059,28 +15102,28 @@
         <v>0.0764</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2559363546165582</v>
+        <v>0.2501742201174324</v>
       </c>
       <c r="J2" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K2" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05146794707786129</v>
+        <v>0.04940420433252712</v>
       </c>
       <c r="M2" t="n">
-        <v>6.419753537082356</v>
+        <v>6.429688573533589</v>
       </c>
       <c r="N2" t="n">
-        <v>65.31671808325399</v>
+        <v>65.39060205633555</v>
       </c>
       <c r="O2" t="n">
-        <v>8.081875901252999</v>
+        <v>8.086445576168527</v>
       </c>
       <c r="P2" t="n">
-        <v>363.8509547673789</v>
+        <v>363.9110484246005</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15137,28 +15180,28 @@
         <v>0.0772</v>
       </c>
       <c r="I3" t="n">
-        <v>0.332956571830804</v>
+        <v>0.3268822284703954</v>
       </c>
       <c r="J3" t="n">
+        <v>330</v>
+      </c>
+      <c r="K3" t="n">
         <v>329</v>
       </c>
-      <c r="K3" t="n">
-        <v>328</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.05710549245316998</v>
+        <v>0.05533990614357387</v>
       </c>
       <c r="M3" t="n">
-        <v>8.180881504053682</v>
+        <v>8.1830341408086</v>
       </c>
       <c r="N3" t="n">
-        <v>99.31750874603271</v>
+        <v>99.31882196121686</v>
       </c>
       <c r="O3" t="n">
-        <v>9.965817013473242</v>
+        <v>9.965882899232604</v>
       </c>
       <c r="P3" t="n">
-        <v>352.6789951979936</v>
+        <v>352.742280393125</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15215,28 +15258,28 @@
         <v>0.0673</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03190446351054063</v>
+        <v>0.02444875300967479</v>
       </c>
       <c r="J4" t="n">
+        <v>330</v>
+      </c>
+      <c r="K4" t="n">
         <v>329</v>
       </c>
-      <c r="K4" t="n">
-        <v>328</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0004084103156675178</v>
+        <v>0.000240645713745935</v>
       </c>
       <c r="M4" t="n">
-        <v>9.586023633993753</v>
+        <v>9.592379215117742</v>
       </c>
       <c r="N4" t="n">
-        <v>134.8145628160154</v>
+        <v>134.8604391523168</v>
       </c>
       <c r="O4" t="n">
-        <v>11.61096735057056</v>
+        <v>11.61294274300519</v>
       </c>
       <c r="P4" t="n">
-        <v>356.2432229140082</v>
+        <v>356.3210619566006</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15293,28 +15336,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2842064820385592</v>
+        <v>0.2749445907119451</v>
       </c>
       <c r="J5" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K5" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02714025120581087</v>
+        <v>0.02549652058962815</v>
       </c>
       <c r="M5" t="n">
-        <v>10.04603034308866</v>
+        <v>10.05844643537949</v>
       </c>
       <c r="N5" t="n">
-        <v>157.0773938481016</v>
+        <v>157.3042696077352</v>
       </c>
       <c r="O5" t="n">
-        <v>12.53305205638681</v>
+        <v>12.54209988828566</v>
       </c>
       <c r="P5" t="n">
-        <v>350.9718936120096</v>
+        <v>351.0685186019757</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15371,28 +15414,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2642888944242902</v>
+        <v>0.2579323889369692</v>
       </c>
       <c r="J6" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K6" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03818572744582993</v>
+        <v>0.03654715740606407</v>
       </c>
       <c r="M6" t="n">
-        <v>7.755822916065289</v>
+        <v>7.758399061681688</v>
       </c>
       <c r="N6" t="n">
-        <v>94.78371864219901</v>
+        <v>94.82415070506035</v>
       </c>
       <c r="O6" t="n">
-        <v>9.735693023210983</v>
+        <v>9.737769287935524</v>
       </c>
       <c r="P6" t="n">
-        <v>350.5884330144497</v>
+        <v>350.6550569531033</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15449,28 +15492,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2078352786686486</v>
+        <v>0.2020563462732745</v>
       </c>
       <c r="J7" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K7" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02732568464805563</v>
+        <v>0.02594971917415845</v>
       </c>
       <c r="M7" t="n">
-        <v>7.147808067493183</v>
+        <v>7.146359303067495</v>
       </c>
       <c r="N7" t="n">
-        <v>82.83630110721185</v>
+        <v>82.85601586907002</v>
       </c>
       <c r="O7" t="n">
-        <v>9.101445001054055</v>
+        <v>9.102527993314276</v>
       </c>
       <c r="P7" t="n">
-        <v>353.7731719117515</v>
+        <v>353.8337421791982</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15527,28 +15570,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1012614798619511</v>
+        <v>0.09107044597984211</v>
       </c>
       <c r="J8" t="n">
+        <v>330</v>
+      </c>
+      <c r="K8" t="n">
         <v>329</v>
       </c>
-      <c r="K8" t="n">
-        <v>328</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.004695408924960787</v>
+        <v>0.003799003557135139</v>
       </c>
       <c r="M8" t="n">
-        <v>8.479715496462475</v>
+        <v>8.500070214188309</v>
       </c>
       <c r="N8" t="n">
-        <v>117.0878666347458</v>
+        <v>117.5776561521749</v>
       </c>
       <c r="O8" t="n">
-        <v>10.820714700737</v>
+        <v>10.84332311388787</v>
       </c>
       <c r="P8" t="n">
-        <v>350.9266094067315</v>
+        <v>351.033307632702</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15586,7 +15629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I330"/>
+  <dimension ref="A1:I331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31063,6 +31106,53 @@
         </is>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>-35.83573772089714,174.5727860747389</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>-35.83636149706036,174.57326431960897</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>-35.836973205546236,174.57377449629783</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-35.83751736877266,174.57439654349173</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-35.83795798240099,174.57513468344786</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-35.83836621121892,174.5758938168061</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>-35.838780785007025,174.57666317473092</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0102/nzd0102.xlsx
+++ b/data/nzd0102/nzd0102.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I331"/>
+  <dimension ref="A1:I332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11345,6 +11345,39 @@
         <v>336.83</v>
       </c>
       <c r="I331" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>362.54</v>
+      </c>
+      <c r="C332" t="n">
+        <v>352.41</v>
+      </c>
+      <c r="D332" t="n">
+        <v>346.76</v>
+      </c>
+      <c r="E332" t="n">
+        <v>346.09</v>
+      </c>
+      <c r="F332" t="n">
+        <v>348.55</v>
+      </c>
+      <c r="G332" t="n">
+        <v>351.35</v>
+      </c>
+      <c r="H332" t="n">
+        <v>337.9</v>
+      </c>
+      <c r="I332" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11361,7 +11394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B357"/>
+  <dimension ref="A1:B358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14934,6 +14967,16 @@
       </c>
       <c r="B357" t="n">
         <v>1.16</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -15102,28 +15145,28 @@
         <v>0.0764</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2501742201174324</v>
+        <v>0.2453579551120934</v>
       </c>
       <c r="J2" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K2" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04940420433252712</v>
+        <v>0.04777913471772199</v>
       </c>
       <c r="M2" t="n">
-        <v>6.429688573533589</v>
+        <v>6.435056882787616</v>
       </c>
       <c r="N2" t="n">
-        <v>65.39060205633555</v>
+        <v>65.38298410942359</v>
       </c>
       <c r="O2" t="n">
-        <v>8.086445576168527</v>
+        <v>8.085974530594539</v>
       </c>
       <c r="P2" t="n">
-        <v>363.9110484246005</v>
+        <v>363.9614706396624</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15180,28 +15223,28 @@
         <v>0.0772</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3268822284703954</v>
+        <v>0.321471703631686</v>
       </c>
       <c r="J3" t="n">
+        <v>331</v>
+      </c>
+      <c r="K3" t="n">
         <v>330</v>
       </c>
-      <c r="K3" t="n">
-        <v>329</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.05533990614357387</v>
+        <v>0.053834079357855</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1830341408086</v>
+        <v>8.182016216171373</v>
       </c>
       <c r="N3" t="n">
-        <v>99.31882196121686</v>
+        <v>99.25844386019254</v>
       </c>
       <c r="O3" t="n">
-        <v>9.965882899232604</v>
+        <v>9.962853198767537</v>
       </c>
       <c r="P3" t="n">
-        <v>352.742280393125</v>
+        <v>352.7988674060545</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15258,28 +15301,28 @@
         <v>0.0673</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02444875300967479</v>
+        <v>0.01827683254491026</v>
       </c>
       <c r="J4" t="n">
+        <v>331</v>
+      </c>
+      <c r="K4" t="n">
         <v>330</v>
       </c>
-      <c r="K4" t="n">
-        <v>329</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.000240645713745935</v>
+        <v>0.0001350773479872336</v>
       </c>
       <c r="M4" t="n">
-        <v>9.592379215117742</v>
+        <v>9.592703011317409</v>
       </c>
       <c r="N4" t="n">
-        <v>134.8604391523168</v>
+        <v>134.7640616585806</v>
       </c>
       <c r="O4" t="n">
-        <v>11.61294274300519</v>
+        <v>11.60879242895576</v>
       </c>
       <c r="P4" t="n">
-        <v>356.3210619566006</v>
+        <v>356.3857464540445</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15336,28 +15379,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2749445907119451</v>
+        <v>0.2675461077271017</v>
       </c>
       <c r="J5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K5" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02549652058962815</v>
+        <v>0.02426416854212021</v>
       </c>
       <c r="M5" t="n">
-        <v>10.05844643537949</v>
+        <v>10.06186051693055</v>
       </c>
       <c r="N5" t="n">
-        <v>157.3042696077352</v>
+        <v>157.2765512976979</v>
       </c>
       <c r="O5" t="n">
-        <v>12.54209988828566</v>
+        <v>12.54099482886816</v>
       </c>
       <c r="P5" t="n">
-        <v>351.0685186019757</v>
+        <v>351.146002633354</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15414,28 +15457,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2579323889369692</v>
+        <v>0.252519800229827</v>
       </c>
       <c r="J6" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K6" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03654715740606407</v>
+        <v>0.03522201965494576</v>
       </c>
       <c r="M6" t="n">
-        <v>7.758399061681688</v>
+        <v>7.757067750225753</v>
       </c>
       <c r="N6" t="n">
-        <v>94.82415070506035</v>
+        <v>94.77480082368285</v>
       </c>
       <c r="O6" t="n">
-        <v>9.737769287935524</v>
+        <v>9.73523501635594</v>
       </c>
       <c r="P6" t="n">
-        <v>350.6550569531033</v>
+        <v>350.7120058356677</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15492,28 +15535,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2020563462732745</v>
+        <v>0.1973071596083335</v>
       </c>
       <c r="J7" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K7" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02594971917415845</v>
+        <v>0.02488080785589808</v>
       </c>
       <c r="M7" t="n">
-        <v>7.146359303067495</v>
+        <v>7.141419435708593</v>
       </c>
       <c r="N7" t="n">
-        <v>82.85601586907002</v>
+        <v>82.78807694727205</v>
       </c>
       <c r="O7" t="n">
-        <v>9.102527993314276</v>
+        <v>9.098795356928962</v>
       </c>
       <c r="P7" t="n">
-        <v>353.8337421791982</v>
+        <v>353.8837110366695</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15570,28 +15613,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09107044597984211</v>
+        <v>0.08164078836851478</v>
       </c>
       <c r="J8" t="n">
+        <v>331</v>
+      </c>
+      <c r="K8" t="n">
         <v>330</v>
       </c>
-      <c r="K8" t="n">
-        <v>329</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.003799003557135139</v>
+        <v>0.003056762460530549</v>
       </c>
       <c r="M8" t="n">
-        <v>8.500070214188309</v>
+        <v>8.516470815340178</v>
       </c>
       <c r="N8" t="n">
-        <v>117.5776561521749</v>
+        <v>117.945517094451</v>
       </c>
       <c r="O8" t="n">
-        <v>10.84332311388787</v>
+        <v>10.86027242266284</v>
       </c>
       <c r="P8" t="n">
-        <v>351.033307632702</v>
+        <v>351.132413207032</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15629,7 +15672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I331"/>
+  <dimension ref="A1:I332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31153,6 +31196,53 @@
         </is>
       </c>
     </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>-35.835729286599936,174.5727987681599</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>-35.83635568421353,174.57327306782298</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>-35.83696130027698,174.57379082573163</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>-35.83749768077796,174.57441832906835</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>-35.8379474338146,174.57514434743578</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>-35.83835357677918,174.57590258566427</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>-35.8387719794659,174.576668007739</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0102/nzd0102.xlsx
+++ b/data/nzd0102/nzd0102.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I332"/>
+  <dimension ref="A1:I333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11380,6 +11380,39 @@
       <c r="I332" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>369.71</v>
+      </c>
+      <c r="C333" t="n">
+        <v>356.75</v>
+      </c>
+      <c r="D333" t="n">
+        <v>356.57</v>
+      </c>
+      <c r="E333" t="n">
+        <v>356.6</v>
+      </c>
+      <c r="F333" t="n">
+        <v>356.5</v>
+      </c>
+      <c r="G333" t="n">
+        <v>359.66</v>
+      </c>
+      <c r="H333" t="n">
+        <v>348.97</v>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11394,7 +11427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B358"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14977,6 +15010,16 @@
       </c>
       <c r="B358" t="n">
         <v>0.75</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -15145,28 +15188,28 @@
         <v>0.0764</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2453579551120934</v>
+        <v>0.2448952169823293</v>
       </c>
       <c r="J2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04777913471772199</v>
+        <v>0.04791274745804042</v>
       </c>
       <c r="M2" t="n">
-        <v>6.435056882787616</v>
+        <v>6.418050727824435</v>
       </c>
       <c r="N2" t="n">
-        <v>65.38298410942359</v>
+        <v>65.18778061825985</v>
       </c>
       <c r="O2" t="n">
-        <v>8.085974530594539</v>
+        <v>8.073895009117956</v>
       </c>
       <c r="P2" t="n">
-        <v>363.9614706396624</v>
+        <v>363.9663471829892</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15223,28 +15266,28 @@
         <v>0.0772</v>
       </c>
       <c r="I3" t="n">
-        <v>0.321471703631686</v>
+        <v>0.3186949713522985</v>
       </c>
       <c r="J3" t="n">
+        <v>332</v>
+      </c>
+      <c r="K3" t="n">
         <v>331</v>
       </c>
-      <c r="K3" t="n">
-        <v>330</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.053834079357855</v>
+        <v>0.05326370967229921</v>
       </c>
       <c r="M3" t="n">
-        <v>8.182016216171373</v>
+        <v>8.16927484970517</v>
       </c>
       <c r="N3" t="n">
-        <v>99.25844386019254</v>
+        <v>99.02120868232527</v>
       </c>
       <c r="O3" t="n">
-        <v>9.962853198767537</v>
+        <v>9.950940090379666</v>
       </c>
       <c r="P3" t="n">
-        <v>352.7988674060545</v>
+        <v>352.828101577198</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15301,28 +15344,28 @@
         <v>0.0673</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01827683254491026</v>
+        <v>0.01809249294319767</v>
       </c>
       <c r="J4" t="n">
+        <v>332</v>
+      </c>
+      <c r="K4" t="n">
         <v>331</v>
       </c>
-      <c r="K4" t="n">
-        <v>330</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0001350773479872336</v>
+        <v>0.0001332598282840491</v>
       </c>
       <c r="M4" t="n">
-        <v>9.592703011317409</v>
+        <v>9.564587527640899</v>
       </c>
       <c r="N4" t="n">
-        <v>134.7640616585806</v>
+        <v>134.3571948509515</v>
       </c>
       <c r="O4" t="n">
-        <v>11.60879242895576</v>
+        <v>11.59125510248789</v>
       </c>
       <c r="P4" t="n">
-        <v>356.3857464540445</v>
+        <v>356.3876912428827</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15379,28 +15422,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2675461077271017</v>
+        <v>0.2665484392678955</v>
       </c>
       <c r="J5" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K5" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02426416854212021</v>
+        <v>0.02424515150150486</v>
       </c>
       <c r="M5" t="n">
-        <v>10.06186051693055</v>
+        <v>10.03587116863113</v>
       </c>
       <c r="N5" t="n">
-        <v>157.2765512976979</v>
+        <v>156.8080512562207</v>
       </c>
       <c r="O5" t="n">
-        <v>12.54099482886816</v>
+        <v>12.52230215480447</v>
       </c>
       <c r="P5" t="n">
-        <v>351.146002633354</v>
+        <v>351.1565208922187</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15457,28 +15500,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>0.252519800229827</v>
+        <v>0.2519663052180339</v>
       </c>
       <c r="J6" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K6" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03522201965494576</v>
+        <v>0.03530095555911061</v>
       </c>
       <c r="M6" t="n">
-        <v>7.757067750225753</v>
+        <v>7.735793215605577</v>
       </c>
       <c r="N6" t="n">
-        <v>94.77480082368285</v>
+        <v>94.49007341887474</v>
       </c>
       <c r="O6" t="n">
-        <v>9.73523501635594</v>
+        <v>9.720600465962725</v>
       </c>
       <c r="P6" t="n">
-        <v>350.7120058356677</v>
+        <v>350.7178680580694</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15535,28 +15578,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1973071596083335</v>
+        <v>0.1976392859128893</v>
       </c>
       <c r="J7" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K7" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02488080785589808</v>
+        <v>0.02512673990925363</v>
       </c>
       <c r="M7" t="n">
-        <v>7.141419435708593</v>
+        <v>7.121895582193313</v>
       </c>
       <c r="N7" t="n">
-        <v>82.78807694727205</v>
+        <v>82.53809296973324</v>
       </c>
       <c r="O7" t="n">
-        <v>9.098795356928962</v>
+        <v>9.085047769259843</v>
       </c>
       <c r="P7" t="n">
-        <v>353.8837110366695</v>
+        <v>353.8801933929305</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15613,28 +15656,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08164078836851478</v>
+        <v>0.07900118572939965</v>
       </c>
       <c r="J8" t="n">
+        <v>332</v>
+      </c>
+      <c r="K8" t="n">
         <v>331</v>
       </c>
-      <c r="K8" t="n">
-        <v>330</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.003056762460530549</v>
+        <v>0.002880793884702304</v>
       </c>
       <c r="M8" t="n">
-        <v>8.516470815340178</v>
+        <v>8.502316373968933</v>
       </c>
       <c r="N8" t="n">
-        <v>117.945517094451</v>
+        <v>117.6452756700936</v>
       </c>
       <c r="O8" t="n">
-        <v>10.86027242266284</v>
+        <v>10.84644069130946</v>
       </c>
       <c r="P8" t="n">
-        <v>351.132413207032</v>
+        <v>351.1603386786667</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15672,7 +15715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I332"/>
+  <dimension ref="A1:I333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31243,6 +31286,53 @@
         </is>
       </c>
     </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>-35.83568842583099,174.57286026260047</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>-35.83633095111337,174.5733102906016</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>-35.83690231504801,174.57387173058146</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>-35.83742729951464,174.57449620871193</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>-35.83788999458139,174.5751969697911</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>-35.8382883642267,174.57594784600067</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>-35.838680879137385,174.5767180089855</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0102/nzd0102.xlsx
+++ b/data/nzd0102/nzd0102.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I333"/>
+  <dimension ref="A1:I334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11413,6 +11413,39 @@
       <c r="I333" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>370.04</v>
+      </c>
+      <c r="C334" t="n">
+        <v>356.16</v>
+      </c>
+      <c r="D334" t="n">
+        <v>357.08</v>
+      </c>
+      <c r="E334" t="n">
+        <v>359.83</v>
+      </c>
+      <c r="F334" t="n">
+        <v>357.15</v>
+      </c>
+      <c r="G334" t="n">
+        <v>359.26</v>
+      </c>
+      <c r="H334" t="n">
+        <v>348.17</v>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11427,7 +11460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B359"/>
+  <dimension ref="A1:B360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15020,6 +15053,16 @@
       </c>
       <c r="B359" t="n">
         <v>0.89</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>-0.65</v>
       </c>
     </row>
   </sheetData>
@@ -15188,28 +15231,28 @@
         <v>0.0764</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2448952169823293</v>
+        <v>0.2446247467659242</v>
       </c>
       <c r="J2" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K2" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04791274745804042</v>
+        <v>0.04812133015791076</v>
       </c>
       <c r="M2" t="n">
-        <v>6.418050727824435</v>
+        <v>6.400148346570964</v>
       </c>
       <c r="N2" t="n">
-        <v>65.18778061825985</v>
+        <v>64.99261173667651</v>
       </c>
       <c r="O2" t="n">
-        <v>8.073895009117956</v>
+        <v>8.061799534637196</v>
       </c>
       <c r="P2" t="n">
-        <v>363.9663471829892</v>
+        <v>363.9692107208306</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15266,28 +15309,28 @@
         <v>0.0772</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3186949713522985</v>
+        <v>0.3155656667355687</v>
       </c>
       <c r="J3" t="n">
+        <v>333</v>
+      </c>
+      <c r="K3" t="n">
         <v>332</v>
       </c>
-      <c r="K3" t="n">
-        <v>331</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.05326370967229921</v>
+        <v>0.05257397884739101</v>
       </c>
       <c r="M3" t="n">
-        <v>8.16927484970517</v>
+        <v>8.15797687810972</v>
       </c>
       <c r="N3" t="n">
-        <v>99.02120868232527</v>
+        <v>98.8022500660916</v>
       </c>
       <c r="O3" t="n">
-        <v>9.950940090379666</v>
+        <v>9.939932095647917</v>
       </c>
       <c r="P3" t="n">
-        <v>352.828101577198</v>
+        <v>352.8612010537063</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15344,28 +15387,28 @@
         <v>0.0673</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01809249294319767</v>
+        <v>0.01822037123329677</v>
       </c>
       <c r="J4" t="n">
+        <v>333</v>
+      </c>
+      <c r="K4" t="n">
         <v>332</v>
       </c>
-      <c r="K4" t="n">
-        <v>331</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0001332598282840491</v>
+        <v>0.0001360685186712063</v>
       </c>
       <c r="M4" t="n">
-        <v>9.564587527640899</v>
+        <v>9.536441768275825</v>
       </c>
       <c r="N4" t="n">
-        <v>134.3571948509515</v>
+        <v>133.9526365896579</v>
       </c>
       <c r="O4" t="n">
-        <v>11.59125510248789</v>
+        <v>11.57379093424699</v>
       </c>
       <c r="P4" t="n">
-        <v>356.3876912428827</v>
+        <v>356.386335856086</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15422,28 +15465,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2665484392678955</v>
+        <v>0.2675047983159083</v>
       </c>
       <c r="J5" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02424515150150486</v>
+        <v>0.02457576207653034</v>
       </c>
       <c r="M5" t="n">
-        <v>10.03587116863113</v>
+        <v>10.01071492572065</v>
       </c>
       <c r="N5" t="n">
-        <v>156.8080512562207</v>
+        <v>156.3417254187034</v>
       </c>
       <c r="O5" t="n">
-        <v>12.52230215480447</v>
+        <v>12.50366847843877</v>
       </c>
       <c r="P5" t="n">
-        <v>351.1565208922187</v>
+        <v>351.1463910885352</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15500,28 +15543,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2519663052180339</v>
+        <v>0.2517982580089332</v>
       </c>
       <c r="J6" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K6" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03530095555911061</v>
+        <v>0.0354868899890719</v>
       </c>
       <c r="M6" t="n">
-        <v>7.735793215605577</v>
+        <v>7.71308994314799</v>
       </c>
       <c r="N6" t="n">
-        <v>94.49007341887474</v>
+        <v>94.20483175291342</v>
       </c>
       <c r="O6" t="n">
-        <v>9.720600465962725</v>
+        <v>9.705917357618157</v>
       </c>
       <c r="P6" t="n">
-        <v>350.7178680580694</v>
+        <v>350.7196561446343</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15578,28 +15621,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1976392859128893</v>
+        <v>0.1977120639225593</v>
       </c>
       <c r="J7" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K7" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02512673990925363</v>
+        <v>0.0253115703526684</v>
       </c>
       <c r="M7" t="n">
-        <v>7.121895582193313</v>
+        <v>7.100838061089485</v>
       </c>
       <c r="N7" t="n">
-        <v>82.53809296973324</v>
+        <v>82.28877571694461</v>
       </c>
       <c r="O7" t="n">
-        <v>9.085047769259843</v>
+        <v>9.07131609618718</v>
       </c>
       <c r="P7" t="n">
-        <v>353.8801933929305</v>
+        <v>353.8794190070778</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15656,28 +15699,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07900118572939965</v>
+        <v>0.07589758300352178</v>
       </c>
       <c r="J8" t="n">
+        <v>333</v>
+      </c>
+      <c r="K8" t="n">
         <v>332</v>
       </c>
-      <c r="K8" t="n">
-        <v>331</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.002880793884702304</v>
+        <v>0.002675794814122723</v>
       </c>
       <c r="M8" t="n">
-        <v>8.502316373968933</v>
+        <v>8.490118534155313</v>
       </c>
       <c r="N8" t="n">
-        <v>117.6452756700936</v>
+        <v>117.3682107675538</v>
       </c>
       <c r="O8" t="n">
-        <v>10.84644069130946</v>
+        <v>10.83366100482906</v>
       </c>
       <c r="P8" t="n">
-        <v>351.1603386786667</v>
+        <v>351.1933247694859</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15715,7 +15758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I333"/>
+  <dimension ref="A1:I334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31333,6 +31376,53 @@
         </is>
       </c>
     </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>-35.8356865452091,174.57286309288702</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>-35.836334313447914,174.57330523036347</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>-35.83689924853622,174.57387593664066</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>-35.83740566948785,174.57452014315143</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>-35.83788529829092,174.5752012722445</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>-35.83829150321874,174.5759456674061</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>-35.83868746272095,174.5767143955297</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0102/nzd0102.xlsx
+++ b/data/nzd0102/nzd0102.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I334"/>
+  <dimension ref="A1:I337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11444,6 +11444,105 @@
         <v>348.17</v>
       </c>
       <c r="I334" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>367.74</v>
+      </c>
+      <c r="C335" t="n">
+        <v>354</v>
+      </c>
+      <c r="D335" t="n">
+        <v>354.02</v>
+      </c>
+      <c r="E335" t="n">
+        <v>356.23</v>
+      </c>
+      <c r="F335" t="n">
+        <v>354.08</v>
+      </c>
+      <c r="G335" t="n">
+        <v>356.25</v>
+      </c>
+      <c r="H335" t="n">
+        <v>344.86</v>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>365.56</v>
+      </c>
+      <c r="C336" t="n">
+        <v>351.95</v>
+      </c>
+      <c r="D336" t="n">
+        <v>349.83</v>
+      </c>
+      <c r="E336" t="n">
+        <v>351.46</v>
+      </c>
+      <c r="F336" t="n">
+        <v>351.29</v>
+      </c>
+      <c r="G336" t="n">
+        <v>353.08</v>
+      </c>
+      <c r="H336" t="n">
+        <v>340.43</v>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>363.52</v>
+      </c>
+      <c r="C337" t="n">
+        <v>349.9</v>
+      </c>
+      <c r="D337" t="n">
+        <v>348.18</v>
+      </c>
+      <c r="E337" t="n">
+        <v>349.06</v>
+      </c>
+      <c r="F337" t="n">
+        <v>349.57</v>
+      </c>
+      <c r="G337" t="n">
+        <v>351.18</v>
+      </c>
+      <c r="H337" t="n">
+        <v>339.65</v>
+      </c>
+      <c r="I337" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11460,7 +11559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B360"/>
+  <dimension ref="A1:B363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15063,6 +15162,36 @@
       </c>
       <c r="B360" t="n">
         <v>-0.65</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>-0.13</v>
       </c>
     </row>
   </sheetData>
@@ -15231,28 +15360,28 @@
         <v>0.0764</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2446247467659242</v>
+        <v>0.2359077434108002</v>
       </c>
       <c r="J2" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K2" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04812133015791076</v>
+        <v>0.04561446463538488</v>
       </c>
       <c r="M2" t="n">
-        <v>6.400148346570964</v>
+        <v>6.386506865415093</v>
       </c>
       <c r="N2" t="n">
-        <v>64.99261173667651</v>
+        <v>64.64676891658914</v>
       </c>
       <c r="O2" t="n">
-        <v>8.061799534637196</v>
+        <v>8.040321443610893</v>
       </c>
       <c r="P2" t="n">
-        <v>363.9692107208306</v>
+        <v>364.0617785223301</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15309,28 +15438,28 @@
         <v>0.0772</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3155656667355687</v>
+        <v>0.2989486311246085</v>
       </c>
       <c r="J3" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K3" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05257397884739101</v>
+        <v>0.04798751852193817</v>
       </c>
       <c r="M3" t="n">
-        <v>8.15797687810972</v>
+        <v>8.154665787925236</v>
       </c>
       <c r="N3" t="n">
-        <v>98.8022500660916</v>
+        <v>98.70121527996841</v>
       </c>
       <c r="O3" t="n">
-        <v>9.939932095647917</v>
+        <v>9.934848528285089</v>
       </c>
       <c r="P3" t="n">
-        <v>352.8612010537063</v>
+        <v>353.0374737432116</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15387,28 +15516,28 @@
         <v>0.0673</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01822037123329677</v>
+        <v>0.007175128110995486</v>
       </c>
       <c r="J4" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K4" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001360685186712063</v>
+        <v>2.146806180658434e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>9.536441768275825</v>
+        <v>9.502962455539773</v>
       </c>
       <c r="N4" t="n">
-        <v>133.9526365896579</v>
+        <v>133.1410570605713</v>
       </c>
       <c r="O4" t="n">
-        <v>11.57379093424699</v>
+        <v>11.53867657318513</v>
       </c>
       <c r="P4" t="n">
-        <v>356.386335856086</v>
+        <v>356.503762137207</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15465,28 +15594,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2675047983159083</v>
+        <v>0.2567367894484744</v>
       </c>
       <c r="J5" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K5" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02457576207653034</v>
+        <v>0.02307127560487188</v>
       </c>
       <c r="M5" t="n">
-        <v>10.01071492572065</v>
+        <v>9.968973608892243</v>
       </c>
       <c r="N5" t="n">
-        <v>156.3417254187034</v>
+        <v>155.3359333188227</v>
       </c>
       <c r="O5" t="n">
-        <v>12.50366847843877</v>
+        <v>12.46338370262357</v>
       </c>
       <c r="P5" t="n">
-        <v>351.1463910885352</v>
+        <v>351.2608050841282</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15543,28 +15672,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2517982580089332</v>
+        <v>0.2414286769167009</v>
       </c>
       <c r="J6" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K6" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0354868899890719</v>
+        <v>0.03324758462472621</v>
       </c>
       <c r="M6" t="n">
-        <v>7.71308994314799</v>
+        <v>7.684331406288312</v>
       </c>
       <c r="N6" t="n">
-        <v>94.20483175291342</v>
+        <v>93.68273424229942</v>
       </c>
       <c r="O6" t="n">
-        <v>9.705917357618157</v>
+        <v>9.678984153427436</v>
       </c>
       <c r="P6" t="n">
-        <v>350.7196561446343</v>
+        <v>350.8303230432967</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15621,28 +15750,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1977120639225593</v>
+        <v>0.1875931826761706</v>
       </c>
       <c r="J7" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K7" t="n">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0253115703526684</v>
+        <v>0.02320863059845868</v>
       </c>
       <c r="M7" t="n">
-        <v>7.100838061089485</v>
+        <v>7.072813325277498</v>
       </c>
       <c r="N7" t="n">
-        <v>82.28877571694461</v>
+        <v>81.86779323901764</v>
       </c>
       <c r="O7" t="n">
-        <v>9.07131609618718</v>
+        <v>9.048082296211593</v>
       </c>
       <c r="P7" t="n">
-        <v>353.8794190070778</v>
+        <v>353.9874142932875</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15699,28 +15828,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07589758300352178</v>
+        <v>0.05520346522931684</v>
       </c>
       <c r="J8" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K8" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002675794814122723</v>
+        <v>0.001431176659184796</v>
       </c>
       <c r="M8" t="n">
-        <v>8.490118534155313</v>
+        <v>8.504236247924352</v>
       </c>
       <c r="N8" t="n">
-        <v>117.3682107675538</v>
+        <v>117.529883241359</v>
       </c>
       <c r="O8" t="n">
-        <v>10.83366100482906</v>
+        <v>10.84112001784682</v>
       </c>
       <c r="P8" t="n">
-        <v>351.1933247694859</v>
+        <v>351.4139029337691</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15758,7 +15887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I334"/>
+  <dimension ref="A1:I337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31423,6 +31552,147 @@
         </is>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>-35.835699652572465,174.57284336664475</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>-35.83634662300991,174.57328670474226</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>-35.8369176476049,174.57385070028036</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>-35.83742977725735,174.57449346699516</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>-35.837907479230765,174.57518095142171</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>-35.83831512413282,174.57592927347673</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>-35.83871470229683,174.57669944485005</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>-35.835712076070514,174.57282466959168</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>-35.836358305693544,174.57326912255016</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>-35.83694284109267,174.57381614459155</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>-35.837461720043294,174.57445812106323</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>-35.83792763715051,174.57516248395416</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>-35.8383400006414,174.5759120080989</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>-35.83875115888664,174.57667943531462</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>-35.83572370172674,174.5728071732615</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>-35.836369988374706,174.57325154035286</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>-35.836952762153274,174.5738025367367</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>-35.837477791881554,174.57444033693588</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>-35.83794006425381,174.57515109898745</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>-35.838354910850484,174.57590165976012</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>-35.83875757787956,174.57667591218916</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0102/nzd0102.xlsx
+++ b/data/nzd0102/nzd0102.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I337"/>
+  <dimension ref="A1:I338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11545,6 +11545,39 @@
       <c r="I337" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>364.01</v>
+      </c>
+      <c r="C338" t="n">
+        <v>348.41</v>
+      </c>
+      <c r="D338" t="n">
+        <v>346</v>
+      </c>
+      <c r="E338" t="n">
+        <v>348.66</v>
+      </c>
+      <c r="F338" t="n">
+        <v>346.15</v>
+      </c>
+      <c r="G338" t="n">
+        <v>348.04</v>
+      </c>
+      <c r="H338" t="n">
+        <v>340.03</v>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B363"/>
+  <dimension ref="A1:B364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15192,6 +15225,16 @@
       </c>
       <c r="B363" t="n">
         <v>-0.13</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -15360,28 +15403,28 @@
         <v>0.0764</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2359077434108002</v>
+        <v>0.2321356098365951</v>
       </c>
       <c r="J2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04561446463538488</v>
+        <v>0.04443386411924222</v>
       </c>
       <c r="M2" t="n">
-        <v>6.386506865415093</v>
+        <v>6.386181799454692</v>
       </c>
       <c r="N2" t="n">
-        <v>64.64676891658914</v>
+        <v>64.57418131367028</v>
       </c>
       <c r="O2" t="n">
-        <v>8.040321443610893</v>
+        <v>8.035806201848716</v>
       </c>
       <c r="P2" t="n">
-        <v>364.0617785223301</v>
+        <v>364.1019735241513</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15438,28 +15481,28 @@
         <v>0.0772</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2989486311246085</v>
+        <v>0.2914691937755653</v>
       </c>
       <c r="J3" t="n">
+        <v>337</v>
+      </c>
+      <c r="K3" t="n">
         <v>336</v>
       </c>
-      <c r="K3" t="n">
-        <v>335</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.04798751852193817</v>
+        <v>0.04580560235486464</v>
       </c>
       <c r="M3" t="n">
-        <v>8.154665787925236</v>
+        <v>8.16146904142737</v>
       </c>
       <c r="N3" t="n">
-        <v>98.70121527996841</v>
+        <v>98.87797727370783</v>
       </c>
       <c r="O3" t="n">
-        <v>9.934848528285089</v>
+        <v>9.943740607724431</v>
       </c>
       <c r="P3" t="n">
-        <v>353.0374737432116</v>
+        <v>353.1171001932813</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15516,28 +15559,28 @@
         <v>0.0673</v>
       </c>
       <c r="I4" t="n">
-        <v>0.007175128110995486</v>
+        <v>0.0008356603652344337</v>
       </c>
       <c r="J4" t="n">
+        <v>337</v>
+      </c>
+      <c r="K4" t="n">
         <v>336</v>
       </c>
-      <c r="K4" t="n">
-        <v>335</v>
-      </c>
       <c r="L4" t="n">
-        <v>2.146806180658434e-05</v>
+        <v>2.923990340963911e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>9.502962455539773</v>
+        <v>9.504320178352279</v>
       </c>
       <c r="N4" t="n">
-        <v>133.1410570605713</v>
+        <v>133.0819474290704</v>
       </c>
       <c r="O4" t="n">
-        <v>11.53867657318513</v>
+        <v>11.53611491920354</v>
       </c>
       <c r="P4" t="n">
-        <v>356.503762137207</v>
+        <v>356.5713905000938</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15594,28 +15637,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2567367894484744</v>
+        <v>0.2511209872760951</v>
       </c>
       <c r="J5" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K5" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02307127560487188</v>
+        <v>0.02220117401164134</v>
       </c>
       <c r="M5" t="n">
-        <v>9.968973608892243</v>
+        <v>9.964070891895974</v>
       </c>
       <c r="N5" t="n">
-        <v>155.3359333188227</v>
+        <v>155.1377606741007</v>
       </c>
       <c r="O5" t="n">
-        <v>12.46338370262357</v>
+        <v>12.45543097103029</v>
       </c>
       <c r="P5" t="n">
-        <v>351.2608050841282</v>
+        <v>351.320675888707</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15672,28 +15715,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2414286769167009</v>
+        <v>0.2347899577383267</v>
       </c>
       <c r="J6" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K6" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03324758462472621</v>
+        <v>0.03158351845571872</v>
       </c>
       <c r="M6" t="n">
-        <v>7.684331406288312</v>
+        <v>7.687026973766263</v>
       </c>
       <c r="N6" t="n">
-        <v>93.68273424229942</v>
+        <v>93.77076230278185</v>
       </c>
       <c r="O6" t="n">
-        <v>9.678984153427436</v>
+        <v>9.683530466869087</v>
       </c>
       <c r="P6" t="n">
-        <v>350.8303230432967</v>
+        <v>350.9014191127462</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15750,28 +15793,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1875931826761706</v>
+        <v>0.1810628984051728</v>
       </c>
       <c r="J7" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K7" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02320863059845868</v>
+        <v>0.02170363963573618</v>
       </c>
       <c r="M7" t="n">
-        <v>7.072813325277498</v>
+        <v>7.074809655183643</v>
       </c>
       <c r="N7" t="n">
-        <v>81.86779323901764</v>
+        <v>81.97917678156773</v>
       </c>
       <c r="O7" t="n">
-        <v>9.048082296211593</v>
+        <v>9.054235295239888</v>
       </c>
       <c r="P7" t="n">
-        <v>353.9874142932875</v>
+        <v>354.0573491002256</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15828,28 +15871,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05520346522931684</v>
+        <v>0.0475538634085247</v>
       </c>
       <c r="J8" t="n">
+        <v>337</v>
+      </c>
+      <c r="K8" t="n">
         <v>336</v>
       </c>
-      <c r="K8" t="n">
-        <v>335</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.001431176659184796</v>
+        <v>0.001065047486464965</v>
       </c>
       <c r="M8" t="n">
-        <v>8.504236247924352</v>
+        <v>8.512175548605223</v>
       </c>
       <c r="N8" t="n">
-        <v>117.529883241359</v>
+        <v>117.6677837987734</v>
       </c>
       <c r="O8" t="n">
-        <v>10.84112001784682</v>
+        <v>10.84747822301448</v>
       </c>
       <c r="P8" t="n">
-        <v>351.4139029337691</v>
+        <v>351.4957304836711</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15887,7 +15930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I337"/>
+  <dimension ref="A1:I338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31693,6 +31736,53 @@
         </is>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>-35.835720909289925,174.5728113758119</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>-35.836378479687774,174.57323876109396</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>-35.83696586997654,174.57378455786875</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>-35.83748047052102,174.57443737291396</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>-35.83796477395621,174.5751284614269</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>-35.83837955193105,174.57588455776033</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>-35.838754450677904,174.57667762858367</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
